--- a/data/credenciales-normalizado.xlsx
+++ b/data/credenciales-normalizado.xlsx
@@ -461,19 +461,19 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>tipo_doc</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>nombre_completo</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>tipo_doc</t>
-        </is>
-      </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>estado</t>
@@ -486,10 +486,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -518,19 +516,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>02/01/26</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>CARDENAS TORRES EDISSON EDGAR</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -543,10 +541,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -575,19 +571,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>03/01/26</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>CARMIN PENA JUAN ELI</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -600,10 +596,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="A4" t="n">
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -632,19 +626,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>05/01/26</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>HURTADO QUISPE WILFREDO</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -657,10 +651,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="A5" t="n">
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -689,19 +681,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>05/01/26</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>CAVERO MOREIRA DARIO FERNANDO</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -714,10 +706,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="A6" t="n">
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -746,19 +736,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>05/01/26</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>QUISPE CHOQUE MIGUEL ALFREDO</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -771,10 +761,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="A7" t="n">
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -803,19 +791,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>06/01/26</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>CRUZ CARI MARCOS ANTONIO</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -828,10 +816,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="A8" t="n">
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -860,19 +846,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>06/01/26</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>GONZALES SUPPO JUAN MIGUEL</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -885,10 +871,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A9" t="n">
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -917,19 +901,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>07/01/26</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>CRUZ CANALES OSCAR OSWALDO</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -942,10 +926,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="A10" t="n">
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -974,19 +956,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>07/01/26</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>ATALAYA LLANOS LUIS ELVIN</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -999,10 +981,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A11" t="n">
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1031,19 +1011,19 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>07/01/26</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>GARCIA MANUYAMA ANGEL</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -1056,10 +1036,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="A12" t="n">
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1088,19 +1066,19 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>07/01/26</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>ASTETE QUISPE STHIN JAVIER</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -1113,10 +1091,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="A13" t="n">
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1145,19 +1121,19 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>08/01/26</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>NAVARRO SICCHA RODOLFO SANTIAGO 27</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -1170,10 +1146,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="A14" t="n">
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1202,19 +1176,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>08/01/26</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>BONILLA CARLOS FELIX</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -1227,10 +1201,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="A15" t="n">
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1259,19 +1231,19 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>08/01/26</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>CHAVEZ MEGIA UBILDORO</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -1284,10 +1256,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="A16" t="n">
+        <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1316,19 +1286,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>08/01/26</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>ROJAS TOVAR MIGUEL ALEXIS</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -1341,10 +1311,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="A17" t="n">
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1373,19 +1341,19 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>08/01/26</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>AJON DIAZ JORGE ROBERTO</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -1398,10 +1366,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="A18" t="n">
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1430,19 +1396,19 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>09/01/26</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>ORTIZ CAMPOS ALCIDES</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -1455,10 +1421,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="A19" t="n">
+        <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1487,19 +1451,19 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
           <t>09/01/26</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>PORRAS PALOMINO SEVERINO</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -1512,10 +1476,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="A20" t="n">
+        <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1544,19 +1506,19 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>09/01/26</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>FLORES QUISPICHITO DANTE</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -1569,10 +1531,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="A21" t="n">
+        <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1601,19 +1561,19 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
           <t>09/01/26</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>NUNEZ MURAYARI VICTOR</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -1626,10 +1586,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="A22" t="n">
+        <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1658,19 +1616,19 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>09/01/26</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>TUESTA VELA ALEX ANTONIO</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -1683,10 +1641,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="A23" t="n">
+        <v>22</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1715,19 +1671,19 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
           <t>10/01/26</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>URIBE ORDAYA LUIS DANIEL</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -1740,10 +1696,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="A24" t="n">
+        <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1772,19 +1726,19 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
           <t>11/01/26</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>GUERRA NINA JIM EMILIO</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -1797,10 +1751,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="A25" t="n">
+        <v>24</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1829,19 +1781,19 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
           <t>11/01/26</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>YANEZ PEREZ JEREMY ALEXIS</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -1854,10 +1806,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+      <c r="A26" t="n">
+        <v>25</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1886,19 +1836,19 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
           <t>12/01/26</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>CISNEROS MOTTA ARGENTINO PEDRO AMERICO</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -1911,10 +1861,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+      <c r="A27" t="n">
+        <v>26</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1943,19 +1891,19 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
           <t>12/01/26</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>ALVAREZ ZEVALLOS JOSE LUIS</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J27" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -1968,10 +1916,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="A28" t="n">
+        <v>27</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2000,19 +1946,19 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
           <t>12/01/26</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>VILCA CALLA JULIO JUAN</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -2025,10 +1971,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="A29" t="n">
+        <v>28</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2057,19 +2001,19 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
           <t>12/01/26</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>CRUZ ALVARADO JORGE LUIS</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J29" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -2082,10 +2026,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+      <c r="A30" t="n">
+        <v>29</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2114,19 +2056,19 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
           <t>13/01/26</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>CORNE DONATO YONEL WILMAN</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J30" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -2139,10 +2081,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="A31" t="n">
+        <v>30</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2171,19 +2111,19 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
           <t>13/01/26</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>ROBERTSON A CACERES JONNHY</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>No Activo</t>
@@ -2191,15 +2131,13 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Datos no coinciden con registro en SUCAMEC</t>
+          <t>Error de login: usuario o clave incorrectos.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
+      <c r="A32" t="n">
+        <v>31</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2228,19 +2166,19 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
           <t>13/01/26</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>GARCES GOMEZ JOSE GABRIEL</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J32" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -2253,10 +2191,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+      <c r="A33" t="n">
+        <v>32</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2285,19 +2221,19 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
           <t>13/01/26</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>LLANOS ACERO ELOY ANTONIO</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J33" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -2310,10 +2246,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
+      <c r="A34" t="n">
+        <v>33</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -2342,19 +2276,19 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
           <t>13/01/26</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>PACHAO HINOJOSA MIJAEL BORIS</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J34" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -2367,10 +2301,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
+      <c r="A35" t="n">
+        <v>34</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -2399,19 +2331,19 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
           <t>13/01/26</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>SALVADOR INGA EDILBERTO</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J35" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -2424,10 +2356,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
+      <c r="A36" t="n">
+        <v>35</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -2456,19 +2386,19 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
           <t>14/01/26</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>BARAHONA MEDINA ADOLFO JAISON</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J36" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -2481,10 +2411,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="A37" t="n">
+        <v>36</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -2513,19 +2441,19 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
           <t>14/01/26</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>VICTORIANO CAMPOS JOSE GABRIEL</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J37" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -2538,10 +2466,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
+      <c r="A38" t="n">
+        <v>37</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -2570,19 +2496,19 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
           <t>15/01/26</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>PALACIOS CORREA FRANCISCO MARCELO</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J38" t="inlineStr">
         <is>
           <t>No Activo</t>
@@ -2590,15 +2516,13 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Datos no coinciden con registro en SUCAMEC</t>
+          <t>Error de login: usuario o clave incorrectos.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
+      <c r="A39" t="n">
+        <v>38</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -2627,19 +2551,19 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
           <t>15/01/26</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>VALDIVIA ZEA FRANKLIN HOOVER</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J39" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -2652,10 +2576,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
+      <c r="A40" t="n">
+        <v>39</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -2684,19 +2606,19 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
           <t>16/01/26</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>HUAMAN RINCON LUIS MODESTO</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J40" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -2709,10 +2631,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+      <c r="A41" t="n">
+        <v>40</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -2741,19 +2661,19 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
           <t>16/01/26</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>GUEVARA PONCE WILDER JAVIER</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J41" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -2766,10 +2686,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
+      <c r="A42" t="n">
+        <v>41</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2798,19 +2716,19 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
           <t>16/01/26</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>MIRANDA CUADROS JUAN CARLOS</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J42" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -2823,10 +2741,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
+      <c r="A43" t="n">
+        <v>42</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2855,19 +2771,19 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
           <t>16/01/26</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>GARCIA CANSINO LEONCIO</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J43" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -2880,10 +2796,8 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
+      <c r="A44" t="n">
+        <v>43</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -2912,19 +2826,19 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
           <t>16/01/26</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>VELASQUEZ ESTOFANERO EDWIN MESIAS</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J44" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -2937,10 +2851,8 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
+      <c r="A45" t="n">
+        <v>44</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2969,19 +2881,19 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
           <t>16/01/26</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>RAMOS DOMINGUEZ WUENNINGUER MANUEL</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J45" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -2994,10 +2906,8 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
+      <c r="A46" t="n">
+        <v>45</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -3026,19 +2936,19 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
           <t>16/01/26</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>QUISPE SILUPU EDINSON</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J46" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -3051,10 +2961,8 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
+      <c r="A47" t="n">
+        <v>46</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -3083,19 +2991,19 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
           <t>17/01/26</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>DIALICO HIPOLO ANDRES</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J47" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -3108,10 +3016,8 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
+      <c r="A48" t="n">
+        <v>47</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -3140,19 +3046,19 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
           <t>17/01/26</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>AMACHE PACCO JAVIER</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J48" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -3165,10 +3071,8 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
+      <c r="A49" t="n">
+        <v>48</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -3197,19 +3101,19 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
           <t>17/01/26</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>GUTIERREZ PEREZ ROQUE WILFREDO</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J49" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -3222,10 +3126,8 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
+      <c r="A50" t="n">
+        <v>49</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -3254,19 +3156,19 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
           <t>17/01/26</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>LLANOS AEDO JUAN LUIS</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J50" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -3279,10 +3181,8 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="A51" t="n">
+        <v>50</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -3311,19 +3211,19 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
           <t>19/01/26</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>REYNOSO JIMENEZ JOSE MARTIN</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J51" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -3336,10 +3236,8 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
+      <c r="A52" t="n">
+        <v>51</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -3368,19 +3266,19 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
           <t>19/01/26</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>CHILQUILLO CANALES EDSON BERNAVE</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J52" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -3393,10 +3291,8 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
+      <c r="A53" t="n">
+        <v>52</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -3425,19 +3321,19 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
           <t>19/01/26</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>ASTOCONDOR BAUTISTA GUILLERMO NELSON</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J53" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -3450,10 +3346,8 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
+      <c r="A54" t="n">
+        <v>53</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -3482,19 +3376,19 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
           <t>19/01/26</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>TORRES SILUPU EDSON MANUEL</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J54" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -3507,10 +3401,8 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
+      <c r="A55" t="n">
+        <v>54</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -3539,19 +3431,19 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
           <t>19/01/26</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>CRUZ VILCA FREDY</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J55" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -3564,10 +3456,8 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+      <c r="A56" t="n">
+        <v>55</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -3596,19 +3486,19 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
           <t>19/01/26</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>CONTRERAS PEREZ DANIEL</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J56" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -3621,10 +3511,8 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
+      <c r="A57" t="n">
+        <v>56</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -3653,19 +3541,19 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
           <t>19/01/26</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>VILCA CRUZ ENRIQUE ALFONSO</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J57" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -3678,10 +3566,8 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
+      <c r="A58" t="n">
+        <v>57</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -3710,19 +3596,19 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
           <t>19/01/26</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>DELGADO GALVEZ ANDERZON WILIAM</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J58" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -3735,10 +3621,8 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
+      <c r="A59" t="n">
+        <v>58</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -3767,19 +3651,19 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
           <t>20/01/26</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>CHAUCCA BEDREGAL VETO</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J59" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -3792,10 +3676,8 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
+      <c r="A60" t="n">
+        <v>59</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -3824,19 +3706,19 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
           <t>20/01/26</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>SANCHEZ BAUTISTA JHAN CARLOS</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J60" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -3849,10 +3731,8 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="A61" t="n">
+        <v>60</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -3881,19 +3761,19 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
           <t>20/01/26</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>MEJIA TAMPE ARTURO FERNANDO</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J61" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -3906,10 +3786,8 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
+      <c r="A62" t="n">
+        <v>61</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -3938,19 +3816,19 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
           <t>20/01/26</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>HUAMAN GUTIERRES ALEX SAUL</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J62" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -3963,10 +3841,8 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
+      <c r="A63" t="n">
+        <v>62</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -3995,19 +3871,19 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
           <t>20/01/26</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>RODRIGUEZ GRANDEZ LUIS ANGEL</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J63" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -4020,10 +3896,8 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
+      <c r="A64" t="n">
+        <v>63</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -4052,19 +3926,19 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
           <t>21/01/26</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>CARMIN RICAPA ELIAS</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J64" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -4077,10 +3951,8 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
+      <c r="A65" t="n">
+        <v>64</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -4109,19 +3981,19 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
           <t>21/01/26</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>PEREZ RAMOS JOSE NICANOR</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J65" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -4134,10 +4006,8 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
+      <c r="A66" t="n">
+        <v>65</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -4166,19 +4036,19 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
           <t>21/01/26</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>QUISPE NURENA ISMAEL ABRAHAM</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J66" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -4191,10 +4061,8 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
+      <c r="A67" t="n">
+        <v>66</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -4223,19 +4091,19 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
           <t>21/01/26</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>POLACK CASTILLO HAROLD</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J67" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -4248,10 +4116,8 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
+      <c r="A68" t="n">
+        <v>67</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -4280,19 +4146,19 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
           <t>22/01/26</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>ARONE LORENZO MIGUEL ANGEL</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J68" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -4305,10 +4171,8 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
+      <c r="A69" t="n">
+        <v>68</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -4337,19 +4201,19 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
           <t>22/01/26</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>ANTON VITE JOSE MARCELINO</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J69" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -4362,10 +4226,8 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
+      <c r="A70" t="n">
+        <v>69</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -4394,19 +4256,19 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
           <t>22/01/26</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>MURGA OCEDA SANTIAGO AVELINO</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J70" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -4419,10 +4281,8 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
+      <c r="A71" t="n">
+        <v>70</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -4451,19 +4311,19 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
           <t>22/01/26</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>VILCA NUNEZ MAYDER KLEIN</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J71" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -4476,10 +4336,8 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
+      <c r="A72" t="n">
+        <v>71</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -4508,19 +4366,19 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
           <t>25/01/26</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>FLORES PINEDA KEVIN PAUL</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J72" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -4533,10 +4391,8 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="A73" t="n">
+        <v>72</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -4565,19 +4421,19 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
           <t>25/01/26</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>FLORES ARIAS BRYAN JOSUE</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J73" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -4590,10 +4446,8 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
+      <c r="A74" t="n">
+        <v>73</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -4622,19 +4476,19 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
           <t>26/01/26</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>LEON ZAVALETA HERBERT RUBEN</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J74" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -4647,10 +4501,8 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
+      <c r="A75" t="n">
+        <v>74</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -4679,19 +4531,19 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
           <t>26/01/26</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>ALARCON ULLOA EDWARD</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J75" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -4704,10 +4556,8 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
+      <c r="A76" t="n">
+        <v>75</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -4736,19 +4586,19 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
           <t>26/01/26</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>CORONEL CHAGUA JUAN ROBERTO</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J76" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -4761,10 +4611,8 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
+      <c r="A77" t="n">
+        <v>76</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -4793,19 +4641,19 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
           <t>26/01/26</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>GOMEZ PEREZ JOSEPH JACINTO</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J77" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -4818,10 +4666,8 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
+      <c r="A78" t="n">
+        <v>77</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -4850,19 +4696,19 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
           <t>27/01/26</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>PASCUAL LUCAS EDUARDO JUAN</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J78" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -4875,10 +4721,8 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
+      <c r="A79" t="n">
+        <v>78</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -4907,19 +4751,19 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
           <t>27/01/26</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>SOBRINO LARRAIN ORLANDO</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J79" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -4932,10 +4776,8 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
+      <c r="A80" t="n">
+        <v>79</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -4964,19 +4806,19 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
           <t>27/01/26</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>TORRES HUARCAYA LUIS ENRIQUE</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J80" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -4989,10 +4831,8 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="A81" t="n">
+        <v>80</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -5021,19 +4861,19 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
           <t>27/01/26</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>LA MADRID RAMIREZ JOSE LUIS</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J81" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -5046,10 +4886,8 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+      <c r="A82" t="n">
+        <v>81</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -5078,19 +4916,19 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
           <t>27/01/26</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>FONSECA SANTOS ALEXANDER</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J82" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -5103,10 +4941,8 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="A83" t="n">
+        <v>82</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -5135,19 +4971,19 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
           <t>28/01/26</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>ANCAJIMA QUISPE GERARDO JACINTO</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J83" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -5160,10 +4996,8 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="A84" t="n">
+        <v>83</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -5192,19 +5026,19 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
           <t>29/01/26</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>GONZALES ALVIS VICTOR</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J84" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -5217,10 +5051,8 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
+      <c r="A85" t="n">
+        <v>84</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -5249,19 +5081,19 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
           <t>29/01/26</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>VIVAR SALAS CARLOS HOOBERT</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J85" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -5274,10 +5106,8 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
+      <c r="A86" t="n">
+        <v>85</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -5306,19 +5136,19 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
           <t>30/01/26</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t>QUILCATE GOICOCHEA HUGO MARTIN</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J86" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -5331,10 +5161,8 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
+      <c r="A87" t="n">
+        <v>86</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -5363,19 +5191,19 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
           <t>01/02/26</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>CUELLER CARDENAS PAULO CESAR</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J87" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -5388,10 +5216,8 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
+      <c r="A88" t="n">
+        <v>87</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -5420,19 +5246,19 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
           <t>02/02/26</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t>MALASQUEZ CORDOVA ROBERTO CARLOS</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J88" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -5445,10 +5271,8 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
+      <c r="A89" t="n">
+        <v>88</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -5477,19 +5301,19 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
           <t>03/02/26</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>MACHACA PACSI DIEGO BERTI</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J89" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -5502,10 +5326,8 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
+      <c r="A90" t="n">
+        <v>89</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -5534,19 +5356,19 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
           <t>03/02/26</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>AUCCA CUSIPUMA IRVIN CRISTOBAL</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J90" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -5559,10 +5381,8 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
+      <c r="A91" t="n">
+        <v>90</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -5591,19 +5411,19 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
           <t>03/02/26</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t>CASTILLO MENDOZA MAGNO SALVATORE</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J91" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -5616,10 +5436,8 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
+      <c r="A92" t="n">
+        <v>91</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -5648,19 +5466,19 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
           <t>03/02/26</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t>CARAZAS LEON DARWIN ROBERT</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J92" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -5673,10 +5491,8 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
+      <c r="A93" t="n">
+        <v>92</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -5705,19 +5521,19 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
           <t>04/02/26</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t>SANCHEZ CAMPOMANES JORGE MARCIANO</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J93" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -5730,10 +5546,8 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
+      <c r="A94" t="n">
+        <v>93</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -5762,19 +5576,19 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
           <t>04/02/26</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t>ALARCON BRYSON ROBERTO SANDRO</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J94" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -5787,10 +5601,8 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
+      <c r="A95" t="n">
+        <v>94</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -5819,19 +5631,19 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
           <t>04/02/26</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t>MARINAS RUEDA PUGLIO RODOLFO</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J95" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -5844,10 +5656,8 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
+      <c r="A96" t="n">
+        <v>95</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -5876,19 +5686,19 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
           <t>04/02/26</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t>BRAVO PUTPANA UBALDO</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J96" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -5901,10 +5711,8 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
+      <c r="A97" t="n">
+        <v>96</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -5933,19 +5741,19 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
           <t>04/02/26</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="I97" t="inlineStr">
         <is>
           <t>ARIVILCA ARIAS JUAN CARLOS</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J97" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -5958,10 +5766,8 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
+      <c r="A98" t="n">
+        <v>97</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -5990,19 +5796,19 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
           <t>05/02/26</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="I98" t="inlineStr">
         <is>
           <t>ORTIZ GUTIERREZ CARLOS ARTURO</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J98" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -6015,10 +5821,8 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
+      <c r="A99" t="n">
+        <v>98</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -6047,19 +5851,19 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
           <t>05/02/26</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t>OCHOA HUALLPARTTUPA MIZRAIM</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J99" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -6072,10 +5876,8 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
+      <c r="A100" t="n">
+        <v>99</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -6104,19 +5906,19 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
           <t>05/02/26</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="I100" t="inlineStr">
         <is>
           <t>TOLEDANO PORTAL LUIS MIGUEL</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J100" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -6129,10 +5931,8 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+      <c r="A101" t="n">
+        <v>100</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -6161,35 +5961,33 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
+          <t>CARNET EXTRANJERIA</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
           <t>06/02/26</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="I101" t="inlineStr">
         <is>
           <t>PALTSEV - MAXIM</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>CARNET EXTRANJERIA</t>
-        </is>
-      </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>No Activo</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>No se pudo completar ingreso de datos/CAPTCHA</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
+      <c r="A102" t="n">
+        <v>101</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -6218,19 +6016,19 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
           <t>06/02/26</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="I102" t="inlineStr">
         <is>
           <t>CASTILLA CARRILLO GERARDO FERMIN</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J102" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -6243,10 +6041,8 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
+      <c r="A103" t="n">
+        <v>102</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -6275,19 +6071,19 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
           <t>06/02/26</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="I103" t="inlineStr">
         <is>
           <t>RODRIGUEZ APAGUENO FREDDY</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J103" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -6300,10 +6096,8 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
+      <c r="A104" t="n">
+        <v>103</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -6332,19 +6126,19 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
           <t>07/02/26</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="I104" t="inlineStr">
         <is>
           <t>VALDIVIA TORRES JESUS FELIPE</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J104" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -6357,10 +6151,8 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
+      <c r="A105" t="n">
+        <v>104</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -6389,19 +6181,19 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
           <t>08/02/26</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="I105" t="inlineStr">
         <is>
           <t>CHAVARRIA INGA HUBERTH ANDY</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J105" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -6414,10 +6206,8 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
+      <c r="A106" t="n">
+        <v>105</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -6446,19 +6236,19 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
           <t>09/02/26</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
+      <c r="I106" t="inlineStr">
         <is>
           <t>PINEDO RODRIGUEZ FEDERMAN</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J106" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -6471,10 +6261,8 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
+      <c r="A107" t="n">
+        <v>106</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -6503,19 +6291,19 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
           <t>09/02/26</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
+      <c r="I107" t="inlineStr">
         <is>
           <t>GUTIERREZ ANORGA RAUL MARCOS</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J107" t="inlineStr">
         <is>
           <t>No Activo</t>
@@ -6523,15 +6311,13 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Datos no coinciden con registro en SUCAMEC</t>
+          <t>Error de login: usuario o clave incorrectos.</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
+      <c r="A108" t="n">
+        <v>107</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -6560,19 +6346,19 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
           <t>09/02/26</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
+      <c r="I108" t="inlineStr">
         <is>
           <t>IGLESIAS GUTIERREZ JESUS ALBERTO</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J108" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -6585,10 +6371,8 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
+      <c r="A109" t="n">
+        <v>108</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -6617,19 +6401,19 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
           <t>09/02/26</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
+      <c r="I109" t="inlineStr">
         <is>
           <t>GOMEZ CHAVARRIA RONNY SERGIO</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J109" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -6642,10 +6426,8 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A110" t="n">
+        <v>109</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -6674,19 +6456,19 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
           <t>09/02/26</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
+      <c r="I110" t="inlineStr">
         <is>
           <t>CONDORI LETONA BRAYAN</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J110" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -6699,10 +6481,8 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
+      <c r="A111" t="n">
+        <v>110</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -6731,19 +6511,19 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
           <t>09/02/26</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
+      <c r="I111" t="inlineStr">
         <is>
           <t>ESPINOZA RUIZ DARIEN MANUEL</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J111" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -6756,10 +6536,8 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
+      <c r="A112" t="n">
+        <v>111</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -6788,19 +6566,19 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
           <t>10/02/26</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
+      <c r="I112" t="inlineStr">
         <is>
           <t>CORNEJO GALLO MARIO GERMAN</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J112" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -6813,10 +6591,8 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
+      <c r="A113" t="n">
+        <v>112</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -6845,19 +6621,19 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
           <t>10/02/26</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
+      <c r="I113" t="inlineStr">
         <is>
           <t>RELUZ FLORES CESAR WILMER</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J113" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -6870,10 +6646,8 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
+      <c r="A114" t="n">
+        <v>113</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -6902,19 +6676,19 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
           <t>10/02/26</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
+      <c r="I114" t="inlineStr">
         <is>
           <t>PIMENTEL PARIONA LUIS MARTIN</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J114" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -6927,10 +6701,8 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
+      <c r="A115" t="n">
+        <v>114</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -6959,19 +6731,19 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
           <t>10/02/26</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
+      <c r="I115" t="inlineStr">
         <is>
           <t>SILVERIO VALDIVIA OSCAR JONATHAN</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J115" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -6984,10 +6756,8 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
+      <c r="A116" t="n">
+        <v>115</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -7016,19 +6786,19 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
           <t>10/02/26</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
+      <c r="I116" t="inlineStr">
         <is>
           <t>CHAISA TORRES SANTOS PALOMINO</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J116" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -7041,10 +6811,8 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
+      <c r="A117" t="n">
+        <v>116</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -7073,19 +6841,19 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
           <t>11/02/26</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
+      <c r="I117" t="inlineStr">
         <is>
           <t>PACHAS MAYANGA ROLANDO FRANCISCO</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J117" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -7098,10 +6866,8 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
+      <c r="A118" t="n">
+        <v>117</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -7130,19 +6896,19 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
           <t>11/02/26</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
+      <c r="I118" t="inlineStr">
         <is>
           <t>MENDOZA RUIZ ROBERTO CAMILO</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J118" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -7155,10 +6921,8 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
+      <c r="A119" t="n">
+        <v>118</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -7187,19 +6951,19 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
           <t>11/02/26</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
+      <c r="I119" t="inlineStr">
         <is>
           <t>USHINAHUA BUENO JOSE ROLIN</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J119" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -7212,10 +6976,8 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
+      <c r="A120" t="n">
+        <v>119</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -7244,19 +7006,19 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
           <t>12/02/26</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
+      <c r="I120" t="inlineStr">
         <is>
           <t>LEON REQUEJO EDY</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J120" t="inlineStr">
         <is>
           <t>No Activo</t>
@@ -7264,15 +7026,13 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Datos no coinciden con registro en SUCAMEC</t>
+          <t>Error de login: usuario o clave incorrectos.</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
+      <c r="A121" t="n">
+        <v>120</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -7301,19 +7061,19 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
           <t>13/02/26</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
+      <c r="I121" t="inlineStr">
         <is>
           <t>MIO SULLON ELIAS</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J121" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -7326,10 +7086,8 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
+      <c r="A122" t="n">
+        <v>121</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -7358,19 +7116,19 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
           <t>14/02/26</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
+      <c r="I122" t="inlineStr">
         <is>
           <t>HUAMAN RAMOS MACARIO EZEQUIEL</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J122" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -7383,10 +7141,8 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
+      <c r="A123" t="n">
+        <v>122</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -7415,19 +7171,19 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
           <t>14/02/26</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
+      <c r="I123" t="inlineStr">
         <is>
           <t>MAGUINA RIVERA EDWIN ROSSER</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J123" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -7440,10 +7196,8 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
+      <c r="A124" t="n">
+        <v>123</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -7472,19 +7226,19 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
           <t>14/02/26</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
+      <c r="I124" t="inlineStr">
         <is>
           <t>INGA CLEMENTE BRAYAN ANTHONY</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J124" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -7497,10 +7251,8 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
+      <c r="A125" t="n">
+        <v>124</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -7529,19 +7281,19 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
           <t>14/02/26</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
+      <c r="I125" t="inlineStr">
         <is>
           <t>UTURUNCO QUISPE JORGE ANTONIO</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J125" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -7554,10 +7306,8 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
+      <c r="A126" t="n">
+        <v>125</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -7586,19 +7336,19 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
           <t>14/02/26</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
+      <c r="I126" t="inlineStr">
         <is>
           <t>SULLCA HUAMANI RUBEN DARIO</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J126" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -7611,10 +7361,8 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
+      <c r="A127" t="n">
+        <v>126</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -7643,19 +7391,19 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
           <t>15/02/26</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
+      <c r="I127" t="inlineStr">
         <is>
           <t>AMACIFUEN YAICATE DAVID</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J127" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -7668,10 +7416,8 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
+      <c r="A128" t="n">
+        <v>127</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -7700,19 +7446,19 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
           <t>16/02/26</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
+      <c r="I128" t="inlineStr">
         <is>
           <t>PERLA ANGULO MARCO ANTONIO</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J128" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -7725,10 +7471,8 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
+      <c r="A129" t="n">
+        <v>128</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -7757,19 +7501,19 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
           <t>17/02/26</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
+      <c r="I129" t="inlineStr">
         <is>
           <t>MONTES BAZALAR ERICK MELQUIADES</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J129" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -7782,10 +7526,8 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
+      <c r="A130" t="n">
+        <v>129</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -7814,19 +7556,19 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
           <t>17/02/26</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
+      <c r="I130" t="inlineStr">
         <is>
           <t>RUIZ FLORES RICHAR</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J130" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -7839,10 +7581,8 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
+      <c r="A131" t="n">
+        <v>130</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -7871,19 +7611,19 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
           <t>17/02/26</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
+      <c r="I131" t="inlineStr">
         <is>
           <t>HUAYANAY CCENCHO AMILKAR</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J131" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -7896,10 +7636,8 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
+      <c r="A132" t="n">
+        <v>131</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -7928,19 +7666,19 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
           <t>18/02/26</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
+      <c r="I132" t="inlineStr">
         <is>
           <t>CASTRILLON ARANA HUMBERTO ORLANDO</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J132" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -7953,10 +7691,8 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
+      <c r="A133" t="n">
+        <v>132</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -7985,19 +7721,19 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
           <t>18/02/26</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
+      <c r="I133" t="inlineStr">
         <is>
           <t>ESTRELLA BAUTISTA FIDEL ANGEL</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J133" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -8010,10 +7746,8 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
+      <c r="A134" t="n">
+        <v>133</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -8042,19 +7776,19 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
           <t>18/02/26</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
+      <c r="I134" t="inlineStr">
         <is>
           <t>BALBIN DE LA CRUZ BENJAMIN SANDRO</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J134" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -8067,10 +7801,8 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
+      <c r="A135" t="n">
+        <v>134</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -8099,19 +7831,19 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
           <t>19/02/26</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
+      <c r="I135" t="inlineStr">
         <is>
           <t>HUANCA CHIPANA WILSON ALCIDES</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J135" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -8124,10 +7856,8 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
+      <c r="A136" t="n">
+        <v>135</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
@@ -8156,19 +7886,19 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
           <t>19/02/26</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
+      <c r="I136" t="inlineStr">
         <is>
           <t>MORALES MALAVER ALEJANDRO</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J136" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -8181,10 +7911,8 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
+      <c r="A137" t="n">
+        <v>136</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -8213,19 +7941,19 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
           <t>19/02/26</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
+      <c r="I137" t="inlineStr">
         <is>
           <t>FERNANDEZ LAURA GILTON YOJAN</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J137" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -8238,10 +7966,8 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
+      <c r="A138" t="n">
+        <v>137</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -8270,19 +7996,19 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
           <t>21/02/26</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
+      <c r="I138" t="inlineStr">
         <is>
           <t>MONTES ALAMO EUGENIO ANIBAL</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J138" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -8295,10 +8021,8 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
+      <c r="A139" t="n">
+        <v>138</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -8327,19 +8051,19 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
           <t>21/02/26</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
+      <c r="I139" t="inlineStr">
         <is>
           <t>RAMIREZ RUIZ CLISMAN TAFERETH</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J139" t="inlineStr">
         <is>
           <t>No Activo</t>
@@ -8347,15 +8071,13 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Datos no coinciden con registro en SUCAMEC</t>
+          <t>Error de login: usuario o clave incorrectos.</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
+      <c r="A140" t="n">
+        <v>139</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -8384,19 +8106,19 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
           <t>21/02/26</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
+      <c r="I140" t="inlineStr">
         <is>
           <t>VARGAS DURAN VICTOR HUGO</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J140" t="inlineStr">
         <is>
           <t>No Activo</t>
@@ -8404,15 +8126,13 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>No registrado en SUCAMEC</t>
+          <t>Error de login: usuario o clave incorrectos.</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
+      <c r="A141" t="n">
+        <v>140</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -8441,19 +8161,19 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
           <t>21/02/26</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
+      <c r="I141" t="inlineStr">
         <is>
           <t>ARONI HUARCA YOSHUA NATAN</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J141" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -8466,10 +8186,8 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
+      <c r="A142" t="n">
+        <v>141</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -8498,19 +8216,19 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
           <t>21/02/26</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
+      <c r="I142" t="inlineStr">
         <is>
           <t>ROBLES VALDIVIESO JUNIOR ALEX</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J142" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -8523,10 +8241,8 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
+      <c r="A143" t="n">
+        <v>142</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -8555,19 +8271,19 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
           <t>23/02/26</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
+      <c r="I143" t="inlineStr">
         <is>
           <t>DIAZ RIOS JUAN HILARIO</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J143" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -8580,10 +8296,8 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
+      <c r="A144" t="n">
+        <v>143</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -8612,19 +8326,19 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
           <t>23/02/26</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
+      <c r="I144" t="inlineStr">
         <is>
           <t>ARROYO ORELLANA DAVID WALTER</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J144" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -8637,10 +8351,8 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
+      <c r="A145" t="n">
+        <v>144</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -8669,19 +8381,19 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
           <t>23/02/26</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
+      <c r="I145" t="inlineStr">
         <is>
           <t>TORRES ROMERO GUIDO ERNESTO</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J145" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -8694,10 +8406,8 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
+      <c r="A146" t="n">
+        <v>145</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -8726,19 +8436,19 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
           <t>25/02/26</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
+      <c r="I146" t="inlineStr">
         <is>
           <t>RIOS RAMIREZ REDER</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J146" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -8751,10 +8461,8 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
+      <c r="A147" t="n">
+        <v>146</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -8783,19 +8491,19 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
           <t>25/02/26</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
+      <c r="I147" t="inlineStr">
         <is>
           <t>LAQUITICONA CCAMA PERCY HUGO</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J147" t="inlineStr">
         <is>
           <t>No Activo</t>
@@ -8803,15 +8511,13 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>No registrado en SUCAMEC</t>
+          <t>Error de login: usuario o clave incorrectos.</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
+      <c r="A148" t="n">
+        <v>147</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -8840,19 +8546,19 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
           <t>26/02/26</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
+      <c r="I148" t="inlineStr">
         <is>
           <t>DE LA CRUZ VERA CRHISTIAN EDGARDO</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J148" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -8865,10 +8571,8 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
+      <c r="A149" t="n">
+        <v>148</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -8897,19 +8601,19 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
           <t>26/02/26</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
+      <c r="I149" t="inlineStr">
         <is>
           <t>RAMIREZ BARBOZA YERSSON</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J149" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -8922,10 +8626,8 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
+      <c r="A150" t="n">
+        <v>149</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -8954,19 +8656,19 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
           <t>26/02/26</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
+      <c r="I150" t="inlineStr">
         <is>
           <t>FERNANDEZ REQUEJO YEREMI HAYRTON</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J150" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -8979,10 +8681,8 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
+      <c r="A151" t="n">
+        <v>150</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -9011,19 +8711,19 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
           <t>27/02/26</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
+      <c r="I151" t="inlineStr">
         <is>
           <t>ARAPA CHILI FREDY ROLANDO</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J151" t="inlineStr">
         <is>
           <t>No Activo</t>
@@ -9031,15 +8731,13 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>Datos no coinciden con registro en SUCAMEC</t>
+          <t>No se pudo confirmar inicio de sesion</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
+      <c r="A152" t="n">
+        <v>151</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -9068,19 +8766,19 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
           <t>27/02/26</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
+      <c r="I152" t="inlineStr">
         <is>
           <t>BLANCO CHUQUIPIONDO EDGAR ENRIQUE</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J152" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -9093,10 +8791,8 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
+      <c r="A153" t="n">
+        <v>152</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -9125,19 +8821,19 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
           <t>27/02/26</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
+      <c r="I153" t="inlineStr">
         <is>
           <t>JUNES CHAVEZ JESUS ELIAS</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J153" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -9150,10 +8846,8 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
+      <c r="A154" t="n">
+        <v>153</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -9182,19 +8876,19 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
           <t>27/02/26</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
+      <c r="I154" t="inlineStr">
         <is>
           <t>DIAZ CHOZO HECTOR SERGIO</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J154" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -9207,10 +8901,8 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
+      <c r="A155" t="n">
+        <v>154</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -9239,19 +8931,19 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
           <t>28/02/26</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
+      <c r="I155" t="inlineStr">
         <is>
           <t>CABRERA GAMARRA RICARDO</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J155" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -9264,10 +8956,8 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
+      <c r="A156" t="n">
+        <v>155</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -9296,19 +8986,19 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
           <t>02/03/26</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
+      <c r="I156" t="inlineStr">
         <is>
           <t>HUISA GIL JOEL EDUARDO</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J156" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -9321,10 +9011,8 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
+      <c r="A157" t="n">
+        <v>156</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -9353,19 +9041,19 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
           <t>02/03/26</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
+      <c r="I157" t="inlineStr">
         <is>
           <t>ROJAS BAUTISTA ARMANDO JORGE</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J157" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -9378,10 +9066,8 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
+      <c r="A158" t="n">
+        <v>157</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -9410,19 +9096,19 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
           <t>02/03/26</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
+      <c r="I158" t="inlineStr">
         <is>
           <t>TAPIA POMA LUIS MIGUEL</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J158" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -9435,10 +9121,8 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
+      <c r="A159" t="n">
+        <v>158</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -9467,19 +9151,19 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
           <t>02/03/26</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
+      <c r="I159" t="inlineStr">
         <is>
           <t>ROSAS SAAVEDRA WILDER</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J159" t="inlineStr">
         <is>
           <t>No Activo</t>
@@ -9487,15 +9171,13 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Datos no coinciden con registro en SUCAMEC</t>
+          <t>Error de login: usuario o clave incorrectos.</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
+      <c r="A160" t="n">
+        <v>159</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -9524,19 +9206,19 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
           <t>02/03/26</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
+      <c r="I160" t="inlineStr">
         <is>
           <t>JHEY JACKSON OCHAVANO SALDANA</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J160" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -9549,10 +9231,8 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
+      <c r="A161" t="n">
+        <v>160</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -9581,19 +9261,19 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
           <t>03/03/26</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
+      <c r="I161" t="inlineStr">
         <is>
           <t>PANANA BERNAL GUSTAVO ENRIQUE</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J161" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -9606,10 +9286,8 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
+      <c r="A162" t="n">
+        <v>161</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -9638,19 +9316,19 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
           <t>03/03/26</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
+      <c r="I162" t="inlineStr">
         <is>
           <t>RODRIGUEZ AYALA GUILLERMO ARTURO</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J162" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -9663,10 +9341,8 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
+      <c r="A163" t="n">
+        <v>162</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -9695,19 +9371,19 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
           <t>03/03/26</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
+      <c r="I163" t="inlineStr">
         <is>
           <t>ARTEAGA TRUJILLO FRANZ ROSEMBERTH</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J163" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -9720,10 +9396,8 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
+      <c r="A164" t="n">
+        <v>163</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -9752,19 +9426,19 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
           <t>05/03/26</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
+      <c r="I164" t="inlineStr">
         <is>
           <t>PURIHUAMAN LUCERO JUAN</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J164" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -9777,10 +9451,8 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
+      <c r="A165" t="n">
+        <v>164</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -9809,19 +9481,19 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
           <t>06/03/26</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
+      <c r="I165" t="inlineStr">
         <is>
           <t>VARGAS ARIAS VICTOR RICARDO</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J165" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -9834,10 +9506,8 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
+      <c r="A166" t="n">
+        <v>165</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -9866,19 +9536,19 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
           <t>06/03/26</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
+      <c r="I166" t="inlineStr">
         <is>
           <t>CCORIMANYA QQUEHUE WILBER</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J166" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -9891,10 +9561,8 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
+      <c r="A167" t="n">
+        <v>166</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -9923,19 +9591,19 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
           <t>08/03/26</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
+      <c r="I167" t="inlineStr">
         <is>
           <t>NAVARRO MAMANI RICHARD</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J167" t="inlineStr">
         <is>
           <t>No Activo</t>
@@ -9943,15 +9611,13 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>Cuenta pendiente de activacion (revisar correo)</t>
+          <t>Error de login: usuario o clave incorrectos.</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
+      <c r="A168" t="n">
+        <v>167</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -9980,19 +9646,19 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
           <t>09/03/26</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
+      <c r="I168" t="inlineStr">
         <is>
           <t>ELIAS BARRIGA ERNESTO HUGO</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J168" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -10005,10 +9671,8 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
+      <c r="A169" t="n">
+        <v>168</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -10037,19 +9701,19 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
           <t>09/03/26</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
+      <c r="I169" t="inlineStr">
         <is>
           <t>MAMANI TICONA YONY EDWIN</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J169" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -10062,10 +9726,8 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
+      <c r="A170" t="n">
+        <v>169</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -10094,19 +9756,19 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
           <t>10/03/26</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
+      <c r="I170" t="inlineStr">
         <is>
           <t>VELASQUEZ OMONTE NICANOR BONIFACIO</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J170" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -10119,10 +9781,8 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
+      <c r="A171" t="n">
+        <v>170</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -10151,19 +9811,19 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
           <t>10/03/26</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
+      <c r="I171" t="inlineStr">
         <is>
           <t>GUTIERREZ CABRERA JOSE LEONARDO</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J171" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -10176,10 +9836,8 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
+      <c r="A172" t="n">
+        <v>171</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -10208,19 +9866,19 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
           <t>11/03/26</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
+      <c r="I172" t="inlineStr">
         <is>
           <t>LITANO GARCIA JHONATAN ALEXANDER</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J172" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -10233,10 +9891,8 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
+      <c r="A173" t="n">
+        <v>172</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -10265,19 +9921,19 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
           <t>12/03/26</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
+      <c r="I173" t="inlineStr">
         <is>
           <t>ROJAS CARHUAMACA MANUEL ANTONIO</t>
         </is>
       </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J173" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -10290,10 +9946,8 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
+      <c r="A174" t="n">
+        <v>173</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -10322,19 +9976,19 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
           <t>12/03/26</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
+      <c r="I174" t="inlineStr">
         <is>
           <t>BALLUMBROSIO FARFAN CHRISTIAN NEZ</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J174" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -10347,10 +10001,8 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
+      <c r="A175" t="n">
+        <v>174</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -10379,19 +10031,19 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
           <t>12/03/26</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
+      <c r="I175" t="inlineStr">
         <is>
           <t>GRADOS TORRES CHRISTIAN</t>
         </is>
       </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J175" t="inlineStr">
         <is>
           <t>No Activo</t>
@@ -10399,15 +10051,13 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>Datos no coinciden con registro en SUCAMEC</t>
+          <t>Error de login: usuario o clave incorrectos.</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
+      <c r="A176" t="n">
+        <v>175</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -10436,19 +10086,19 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
           <t>12/03/26</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
+      <c r="I176" t="inlineStr">
         <is>
           <t>CANTARO DIAZ RENE LEONEL</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J176" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -10461,10 +10111,8 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
+      <c r="A177" t="n">
+        <v>176</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -10493,19 +10141,19 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
           <t>12/03/26</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
+      <c r="I177" t="inlineStr">
         <is>
           <t>MAMANI CALIZAYA ORESTES PEDRO</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J177" t="inlineStr">
         <is>
           <t>No Activo</t>
@@ -10513,15 +10161,13 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>Datos no coinciden con registro en SUCAMEC</t>
+          <t>Error de login: usuario o clave incorrectos.</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
+      <c r="A178" t="n">
+        <v>177</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -10550,19 +10196,19 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
           <t>13/03/26</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
+      <c r="I178" t="inlineStr">
         <is>
           <t>HERRERA CARRILLO MARTIN HUMBERTO</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J178" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -10575,10 +10221,8 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
+      <c r="A179" t="n">
+        <v>178</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -10607,19 +10251,19 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
           <t>13/03/26</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
+      <c r="I179" t="inlineStr">
         <is>
           <t>CONDORI JIMENEZ DAVID ISAAC</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J179" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -10632,10 +10276,8 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
+      <c r="A180" t="n">
+        <v>179</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -10664,19 +10306,19 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
           <t>13/03/26</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
+      <c r="I180" t="inlineStr">
         <is>
           <t>ALEGRIA LLERENA DANIEL</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J180" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -10689,10 +10331,8 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
+      <c r="A181" t="n">
+        <v>180</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -10721,19 +10361,19 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
           <t>13/03/26</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
+      <c r="I181" t="inlineStr">
         <is>
           <t>TTITO POLO FRANK ANDI</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J181" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -10746,10 +10386,8 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
+      <c r="A182" t="n">
+        <v>181</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -10778,19 +10416,19 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
           <t>14/03/26</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
+      <c r="I182" t="inlineStr">
         <is>
           <t>HUARACA ORDONEZ MANUEL JORDANO</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J182" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -10803,10 +10441,8 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
+      <c r="A183" t="n">
+        <v>182</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -10835,19 +10471,19 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
           <t>16/03/26</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
+      <c r="I183" t="inlineStr">
         <is>
           <t>MAYTA ZARATE WILLIAM PABLO</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J183" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -10860,10 +10496,8 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
+      <c r="A184" t="n">
+        <v>183</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -10892,19 +10526,19 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
           <t>16/03/26</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
+      <c r="I184" t="inlineStr">
         <is>
           <t>ABAD MORILLO DARWIN FRIEDMAN</t>
         </is>
       </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J184" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -10917,10 +10551,8 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
+      <c r="A185" t="n">
+        <v>184</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -10949,19 +10581,19 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
           <t>16/03/26</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
+      <c r="I185" t="inlineStr">
         <is>
           <t>ROMO LUYO CARLOS LORENZO</t>
         </is>
       </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J185" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -10974,10 +10606,8 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
+      <c r="A186" t="n">
+        <v>185</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -11006,19 +10636,19 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
           <t>17/03/26</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
+      <c r="I186" t="inlineStr">
         <is>
           <t>OSCCO CCORISONCCO SAUL SIMEON</t>
         </is>
       </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J186" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -11031,10 +10661,8 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
+      <c r="A187" t="n">
+        <v>186</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -11063,19 +10691,19 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
           <t>17/03/26</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
+      <c r="I187" t="inlineStr">
         <is>
           <t>JULCA RODRIGUEZ CLAUS SILVESTRE</t>
         </is>
       </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J187" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -11088,10 +10716,8 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
+      <c r="A188" t="n">
+        <v>187</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -11120,19 +10746,19 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
           <t>17/03/26</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
+      <c r="I188" t="inlineStr">
         <is>
           <t>HUAMAN CONDOR ERICK</t>
         </is>
       </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J188" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -11145,10 +10771,8 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="A189" t="n">
+        <v>188</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -11177,19 +10801,19 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
           <t>18/03/26</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
+      <c r="I189" t="inlineStr">
         <is>
           <t>VALQUI TAPIA CARLOS ANTONIO</t>
         </is>
       </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J189" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -11202,10 +10826,8 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
+      <c r="A190" t="n">
+        <v>189</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -11234,19 +10856,19 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
           <t>18/03/26</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
+      <c r="I190" t="inlineStr">
         <is>
           <t>DE LA CRUZ FLORES ALAN JHON</t>
         </is>
       </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J190" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -11259,10 +10881,8 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
+      <c r="A191" t="n">
+        <v>190</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -11291,19 +10911,19 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
           <t>18/03/26</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
+      <c r="I191" t="inlineStr">
         <is>
           <t>ALVARO ARIAS JHAN CARLOS</t>
         </is>
       </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J191" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -11316,10 +10936,8 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
+      <c r="A192" t="n">
+        <v>191</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -11348,19 +10966,19 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
           <t>18/03/26</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
+      <c r="I192" t="inlineStr">
         <is>
           <t>VILCA RAMIREZ NAYDELYN MALLERLY</t>
         </is>
       </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J192" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -11373,10 +10991,8 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
+      <c r="A193" t="n">
+        <v>192</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -11405,19 +11021,19 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
           <t>19/03/26</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
+      <c r="I193" t="inlineStr">
         <is>
           <t>VILLODAS BERNACHEA JORGE LUIS</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J193" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -11430,10 +11046,8 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
+      <c r="A194" t="n">
+        <v>193</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -11462,19 +11076,19 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
           <t>20/03/26</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
+      <c r="I194" t="inlineStr">
         <is>
           <t>QUILICHE MEDINA LUIS</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J194" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -11487,10 +11101,8 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
+      <c r="A195" t="n">
+        <v>194</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -11519,19 +11131,19 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
           <t>20/03/26</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
+      <c r="I195" t="inlineStr">
         <is>
           <t>DIAZ DE LA CRUZ JOHAN ALEXANDER</t>
         </is>
       </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J195" t="inlineStr">
         <is>
           <t>No Activo</t>
@@ -11539,15 +11151,13 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>No registrado en SUCAMEC</t>
+          <t>Error de login: usuario o clave incorrectos.</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
+      <c r="A196" t="n">
+        <v>195</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -11576,19 +11186,19 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
           <t>23/03/26</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
+      <c r="I196" t="inlineStr">
         <is>
           <t>MEJIA SALCEDO JORGE ANTONIO</t>
         </is>
       </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J196" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -11601,10 +11211,8 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
+      <c r="A197" t="n">
+        <v>196</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -11633,19 +11241,19 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
           <t>23/03/26</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
+      <c r="I197" t="inlineStr">
         <is>
           <t>CHAVEZ CHACON SANDRO ALDAIR</t>
         </is>
       </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
       <c r="J197" t="inlineStr">
         <is>
           <t>No Activo</t>
@@ -11653,7 +11261,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>Cuenta pendiente de activacion (revisar correo)</t>
+          <t>Error de login: usuario o clave incorrectos.</t>
         </is>
       </c>
     </row>
